--- a/public/data/Template Colisage.xlsx
+++ b/public/data/Template Colisage.xlsx
@@ -1,20 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PREDOUANE\TEMPLATES  CLIENT\CM260045\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJET NEXT JS\SFX_PreDouane\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F540528-1357-4D06-8100-8F27C93CC599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{637418B6-88B6-4445-BDE8-A4454AD084B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Colisages" sheetId="1" r:id="rId1"/>
-    <sheet name="Feuil1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Colisages!$A$1:$Q$1</definedName>
@@ -34,24 +33,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>tc={DB30A2CE-F783-41BF-B75B-6535FA68E849}</author>
-  </authors>
-  <commentList>
-    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{DB30A2CE-F783-41BF-B75B-6535FA68E849}">
-      <text>
-        <t>[Commentaire à thread]
-Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
-Commentaire :
-    Valeur entre 0 et 1, -1, -2</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -198,9 +179,7 @@
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="SOFTRONIC - Edwin Fom" id="{65AE4025-A621-4CFB-8490-E03AAE93E9F2}" userId="S::edwin.fom@softronic-cm.com::4b702ed5-3129-4f37-80f9-05cca8247537" providerId="AD"/>
-</personList>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -523,18 +502,10 @@
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="P1" dT="2026-02-16T16:09:57.94" personId="{65AE4025-A621-4CFB-8490-E03AAE93E9F2}" id="{DB30A2CE-F783-41BF-B75B-6535FA68E849}">
-    <text>Valeur entre 0 et 1, -1, -2</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q166"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.796875" customWidth="1"/>
     <col min="2" max="2" width="15.296875" customWidth="1"/>
@@ -545,8 +516,7 @@
     <col min="7" max="8" width="10.796875" customWidth="1"/>
     <col min="9" max="11" width="15.796875" customWidth="1"/>
     <col min="12" max="12" width="10.796875" customWidth="1"/>
-    <col min="13" max="15" width="15.796875" customWidth="1"/>
-    <col min="16" max="16" width="20.796875" customWidth="1"/>
+    <col min="13" max="16" width="15.796875" customWidth="1"/>
     <col min="17" max="17" width="24.8984375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -617,27 +587,5 @@
   <ignoredErrors>
     <ignoredError sqref="A1:O1 Q1" numberStoredAsText="1"/>
   </ignoredErrors>
-  <legacyDrawing r:id="rId2"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{91DC21CF-9321-4E91-8F4A-028F95706F67}">
-          <x14:formula1>
-            <xm:f>Feuil1!$A$2:$A$13</xm:f>
-          </x14:formula1>
-          <xm:sqref>P1:P1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE6A97BF-F9F0-409F-A705-132DD07F5B30}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>